--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_14_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_14_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60788.53090317619</v>
+        <v>60796.75029263232</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23532528.5400515</v>
+        <v>23540750.25461933</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3186504.601055079</v>
+        <v>3183079.072461132</v>
       </c>
     </row>
     <row r="11">
@@ -22519,49 +22519,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G2" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H2" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I2" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J2" t="n">
-        <v>71.86158291864608</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K2" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L2" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M2" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P2" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q2" t="n">
-        <v>83.38548886942439</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R2" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S2" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T2" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U2" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V2" t="n">
         <v>327.7522584701349</v>
@@ -22598,19 +22598,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H3" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I3" t="n">
-        <v>75.82426679245283</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J3" t="n">
-        <v>61.80819270440254</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K3" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -22625,22 +22625,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q3" t="n">
-        <v>52.12064201054982</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R3" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S3" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T3" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U3" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V3" t="n">
         <v>232.8005871494253</v>
@@ -22677,49 +22677,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H4" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I4" t="n">
-        <v>138.0970323043075</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J4" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K4" t="n">
-        <v>61.97063521971575</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L4" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M4" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N4" t="n">
-        <v>39.38128217015118</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O4" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P4" t="n">
-        <v>67.9365286393116</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q4" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R4" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S4" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T4" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U4" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V4" t="n">
         <v>252.137643323828</v>
@@ -22756,49 +22756,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H5" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I5" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J5" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K5" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L5" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M5" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P5" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q5" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R5" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S5" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T5" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U5" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22835,19 +22835,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H6" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I6" t="n">
-        <v>75.82426679245283</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J6" t="n">
-        <v>61.80819270440254</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K6" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -22862,22 +22862,22 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q6" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R6" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S6" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T6" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U6" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -22914,49 +22914,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H7" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I7" t="n">
-        <v>138.0970323043075</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J7" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K7" t="n">
-        <v>61.97063521971575</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L7" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M7" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N7" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O7" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P7" t="n">
-        <v>67.9365286393116</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q7" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R7" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S7" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T7" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U7" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -22993,49 +22993,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>413.992184751316</v>
+        <v>413.9914553764875</v>
       </c>
       <c r="H8" t="n">
-        <v>326.0531036233048</v>
+        <v>326.0456339133427</v>
       </c>
       <c r="I8" t="n">
-        <v>159.9508041432702</v>
+        <v>159.9226849201952</v>
       </c>
       <c r="J8" t="n">
-        <v>69.81437688849532</v>
+        <v>69.75247211164648</v>
       </c>
       <c r="K8" t="n">
-        <v>53.38262491432727</v>
+        <v>53.28984570098882</v>
       </c>
       <c r="L8" t="n">
-        <v>28.9513596936053</v>
+        <v>28.8362588753597</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2246352373229854</v>
+        <v>0.09656339947136416</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>9.284814436762105</v>
+        <v>9.161922983629779</v>
       </c>
       <c r="P8" t="n">
-        <v>42.77387012712884</v>
+        <v>42.66898511507466</v>
       </c>
       <c r="Q8" t="n">
-        <v>80.78073510058016</v>
+        <v>80.70197082457096</v>
       </c>
       <c r="R8" t="n">
-        <v>133.2615277638808</v>
+        <v>133.2157111723112</v>
       </c>
       <c r="S8" t="n">
-        <v>179.1558484807177</v>
+        <v>179.1392278518137</v>
       </c>
       <c r="T8" t="n">
-        <v>217.3589048405133</v>
+        <v>217.3557120022016</v>
       </c>
       <c r="U8" t="n">
-        <v>251.240808686731</v>
+        <v>251.2407503367447</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,19 +23072,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>136.6423096160408</v>
+        <v>136.6419193661031</v>
       </c>
       <c r="H9" t="n">
-        <v>105.4632555572512</v>
+        <v>105.4594865644317</v>
       </c>
       <c r="I9" t="n">
-        <v>75.37992716981131</v>
+        <v>75.36649093292084</v>
       </c>
       <c r="J9" t="n">
-        <v>60.58889081761008</v>
+        <v>60.55202075660908</v>
       </c>
       <c r="K9" t="n">
-        <v>24.61179746492502</v>
+        <v>24.54878065809741</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -23099,22 +23099,22 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.07452062187741149</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.47324578413472</v>
+        <v>50.42343072191045</v>
       </c>
       <c r="R9" t="n">
-        <v>102.1431266054734</v>
+        <v>102.1188968768846</v>
       </c>
       <c r="S9" t="n">
-        <v>158.6585484623284</v>
+        <v>158.6512997408977</v>
       </c>
       <c r="T9" t="n">
-        <v>197.3383702042556</v>
+        <v>197.336797223147</v>
       </c>
       <c r="U9" t="n">
-        <v>225.8952500055031</v>
+        <v>225.8952243311651</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,49 +23151,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.4031105059997</v>
+        <v>167.4027833335613</v>
       </c>
       <c r="H10" t="n">
-        <v>157.0004839828494</v>
+        <v>156.9975751224423</v>
       </c>
       <c r="I10" t="n">
-        <v>137.7716552551271</v>
+        <v>137.761816287615</v>
       </c>
       <c r="J10" t="n">
-        <v>85.43309357054366</v>
+        <v>85.40996247914654</v>
       </c>
       <c r="K10" t="n">
-        <v>60.71358603938786</v>
+        <v>60.67557455063191</v>
       </c>
       <c r="L10" t="n">
-        <v>47.48461070746779</v>
+        <v>47.4359690887577</v>
       </c>
       <c r="M10" t="n">
-        <v>46.77466919350671</v>
+        <v>46.72338342663512</v>
       </c>
       <c r="N10" t="n">
-        <v>37.72557725211838</v>
+        <v>37.67551094615366</v>
       </c>
       <c r="O10" t="n">
-        <v>55.36394828790834</v>
+        <v>55.31770395088348</v>
       </c>
       <c r="P10" t="n">
-        <v>66.62793847537716</v>
+        <v>66.5883684560963</v>
       </c>
       <c r="Q10" t="n">
-        <v>102.2790016294458</v>
+        <v>102.2516053991695</v>
       </c>
       <c r="R10" t="n">
-        <v>150.8606700656941</v>
+        <v>150.8459592031442</v>
       </c>
       <c r="S10" t="n">
-        <v>213.7716472173001</v>
+        <v>213.7659454939867</v>
       </c>
       <c r="T10" t="n">
-        <v>225.433786149593</v>
+        <v>225.4323882309924</v>
       </c>
       <c r="U10" t="n">
-        <v>286.2869637827204</v>
+        <v>286.286945936951</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,22 +23230,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H11" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I11" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J11" t="n">
-        <v>69.47317588347013</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K11" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L11" t="n">
-        <v>28.31695768355505</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -23254,25 +23254,25 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8.607472728219301</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P11" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q11" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R11" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S11" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T11" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,19 +23309,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H12" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I12" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J12" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K12" t="n">
-        <v>24.26446727624578</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -23339,19 +23339,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.19867974639887</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R12" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S12" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T12" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U12" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,49 +23388,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H13" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I13" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J13" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K13" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L13" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M13" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N13" t="n">
-        <v>37.44962643244625</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O13" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P13" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q13" t="n">
-        <v>102.1280016294458</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R13" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S13" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T13" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,22 +23467,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H14" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I14" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J14" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K14" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L14" t="n">
-        <v>28.31695768355505</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -23491,25 +23491,25 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8.607472728219392</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P14" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q14" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R14" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S14" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T14" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,19 +23546,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H15" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I15" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J15" t="n">
-        <v>60.38567383647804</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K15" t="n">
-        <v>24.26446727624578</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -23576,19 +23576,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>50.19867974639887</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R15" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S15" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T15" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U15" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,49 +23625,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H16" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I16" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J16" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K16" t="n">
-        <v>60.50407784266664</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L16" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M16" t="n">
-        <v>46.49199706235908</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N16" t="n">
-        <v>37.44962643244625</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O16" t="n">
-        <v>55.10906304200678</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P16" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q16" t="n">
-        <v>102.1280016294458</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R16" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S16" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T16" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,22 +23704,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H17" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I17" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J17" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K17" t="n">
-        <v>52.87125305503078</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L17" t="n">
-        <v>28.31695768355505</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -23728,25 +23728,25 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>8.607472728219395</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P17" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q17" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R17" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S17" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T17" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,19 +23783,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H18" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I18" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J18" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K18" t="n">
-        <v>24.26446727624579</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -23813,19 +23813,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>50.19867974639886</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R18" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S18" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T18" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U18" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,49 +23862,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H19" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I19" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J19" t="n">
-        <v>85.30560176726497</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K19" t="n">
-        <v>60.50407784266653</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L19" t="n">
-        <v>47.21651234681204</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M19" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N19" t="n">
-        <v>37.44962643244624</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O19" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P19" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q19" t="n">
-        <v>102.1280016294458</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R19" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S19" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T19" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,22 +23941,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H20" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I20" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J20" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K20" t="n">
-        <v>52.87125305503072</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L20" t="n">
-        <v>28.31695768355505</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -23965,25 +23965,25 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>8.607472728219392</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P20" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R20" t="n">
-        <v>133.00900012569</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S20" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T20" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,19 +24020,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H21" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I21" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J21" t="n">
-        <v>60.38567383647791</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K21" t="n">
-        <v>24.26446727624578</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -24050,19 +24050,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.19867974639887</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R21" t="n">
-        <v>102.0095794356621</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S21" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T21" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U21" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,49 +24099,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H22" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I22" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J22" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K22" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L22" t="n">
-        <v>47.21651234681212</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M22" t="n">
-        <v>46.49199706235921</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N22" t="n">
-        <v>37.44962643244627</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O22" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P22" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.1280016294459</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R22" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S22" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T22" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,22 +24178,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H23" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I23" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J23" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K23" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L23" t="n">
-        <v>28.31695768355513</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -24202,25 +24202,25 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>8.607472728219392</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P23" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q23" t="n">
-        <v>80.3466094724394</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R23" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S23" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T23" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,19 +24257,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H24" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I24" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J24" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K24" t="n">
-        <v>24.26446727624566</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -24287,19 +24287,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>50.19867974639887</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R24" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S24" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T24" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U24" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,49 +24336,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H25" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I25" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J25" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K25" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L25" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M25" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N25" t="n">
-        <v>37.44962643244613</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O25" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P25" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q25" t="n">
-        <v>102.1280016294458</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R25" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S25" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T25" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,22 +24415,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H26" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I26" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J26" t="n">
-        <v>69.47317588347012</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K26" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L26" t="n">
-        <v>28.31695768355511</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -24439,25 +24439,25 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>8.607472728219388</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P26" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q26" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R26" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S26" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T26" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,19 +24494,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H27" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I27" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J27" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K27" t="n">
-        <v>24.26446727624578</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -24524,19 +24524,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>50.19867974639892</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R27" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S27" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T27" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U27" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,49 +24573,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H28" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I28" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J28" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K28" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L28" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M28" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N28" t="n">
-        <v>37.44962643244625</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O28" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P28" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q28" t="n">
-        <v>102.1280016294457</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R28" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S28" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T28" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,22 +24652,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H29" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I29" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J29" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K29" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L29" t="n">
-        <v>28.31695768355505</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -24676,25 +24676,25 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>8.607472728219392</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P29" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q29" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R29" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S29" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T29" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,19 +24731,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H30" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I30" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J30" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K30" t="n">
-        <v>24.26446727624578</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -24761,19 +24761,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.19867974639887</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R30" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S30" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T30" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U30" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,49 +24810,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H31" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I31" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J31" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K31" t="n">
-        <v>60.50407784266662</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L31" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M31" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N31" t="n">
-        <v>37.44962643244625</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O31" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P31" t="n">
-        <v>66.40984011472149</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q31" t="n">
-        <v>102.1280016294459</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R31" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S31" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T31" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,22 +24889,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H32" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I32" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J32" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K32" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L32" t="n">
-        <v>28.31695768355503</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -24913,25 +24913,25 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>8.607472728219378</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P32" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q32" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R32" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S32" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T32" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,19 +24968,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H33" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I33" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J33" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K33" t="n">
-        <v>24.26446727624579</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -24998,19 +24998,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>50.19867974639887</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R33" t="n">
-        <v>102.0095794356621</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S33" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T33" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U33" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,49 +25047,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H34" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I34" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J34" t="n">
-        <v>85.30560176726497</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K34" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L34" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M34" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N34" t="n">
-        <v>37.44962643244624</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O34" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P34" t="n">
-        <v>66.40984011472143</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q34" t="n">
-        <v>102.1280016294458</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R34" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S34" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T34" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,22 +25126,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H35" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I35" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J35" t="n">
-        <v>69.47317588347026</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K35" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L35" t="n">
-        <v>28.31695768355514</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -25150,25 +25150,25 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>8.607472728219392</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P35" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q35" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R35" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S35" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T35" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,19 +25205,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H36" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I36" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J36" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K36" t="n">
-        <v>24.26446727624578</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -25235,19 +25235,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>50.19867974639891</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R36" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S36" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T36" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U36" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,49 +25284,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H37" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I37" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J37" t="n">
-        <v>85.30560176726505</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K37" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L37" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M37" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N37" t="n">
-        <v>37.44962643244625</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O37" t="n">
-        <v>55.10906304200672</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P37" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q37" t="n">
-        <v>102.1280016294457</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R37" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S37" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T37" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,22 +25363,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H38" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I38" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J38" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K38" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L38" t="n">
-        <v>28.31695768355514</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -25387,25 +25387,25 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>8.607472728219392</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P38" t="n">
-        <v>42.19577464974191</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q38" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R38" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S38" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T38" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,19 +25442,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H39" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I39" t="n">
-        <v>75.30587056603777</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J39" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K39" t="n">
-        <v>24.26446727624585</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -25472,19 +25472,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>50.19867974639875</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R39" t="n">
-        <v>102.009579435662</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S39" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T39" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U39" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,49 +25521,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H40" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I40" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J40" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K40" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L40" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M40" t="n">
-        <v>46.49199706235924</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N40" t="n">
-        <v>37.44962643244632</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O40" t="n">
-        <v>55.10906304200651</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P40" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q40" t="n">
-        <v>102.1280016294458</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R40" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S40" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T40" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,22 +25600,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H41" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I41" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J41" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K41" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L41" t="n">
-        <v>28.31695768355505</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -25624,25 +25624,25 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>8.607472728219479</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P41" t="n">
-        <v>42.19577464974201</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q41" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R41" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S41" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T41" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,19 +25679,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H42" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I42" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J42" t="n">
-        <v>60.38567383647786</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K42" t="n">
-        <v>24.26446727624569</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -25709,19 +25709,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>50.19867974639875</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R42" t="n">
-        <v>102.0095794356619</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S42" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T42" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U42" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,49 +25758,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H43" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I43" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J43" t="n">
-        <v>85.30560176726487</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K43" t="n">
-        <v>60.50407784266659</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L43" t="n">
-        <v>47.21651234681187</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M43" t="n">
-        <v>46.49199706235924</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N43" t="n">
-        <v>37.44962643244625</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O43" t="n">
-        <v>55.10906304200653</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P43" t="n">
-        <v>66.40984011472116</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q43" t="n">
-        <v>102.1280016294459</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R43" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S43" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T43" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,22 +25837,22 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>413.9881646508134</v>
+        <v>413.9909054436208</v>
       </c>
       <c r="H44" t="n">
-        <v>326.0119327690335</v>
+        <v>326.0400019133721</v>
       </c>
       <c r="I44" t="n">
-        <v>159.7958192186471</v>
+        <v>159.9014836333536</v>
       </c>
       <c r="J44" t="n">
-        <v>69.47317588347019</v>
+        <v>69.70579724700553</v>
       </c>
       <c r="K44" t="n">
-        <v>52.87125305503079</v>
+        <v>53.21989217810253</v>
       </c>
       <c r="L44" t="n">
-        <v>28.31695768355505</v>
+        <v>28.74947534450564</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -25861,25 +25861,25 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>8.607472728219392</v>
+        <v>9.069265482343809</v>
       </c>
       <c r="P44" t="n">
-        <v>42.195774649742</v>
+        <v>42.58990408143413</v>
       </c>
       <c r="Q44" t="n">
-        <v>80.34660947243944</v>
+        <v>80.64258426171739</v>
       </c>
       <c r="R44" t="n">
-        <v>133.0090001256899</v>
+        <v>133.1811664518765</v>
       </c>
       <c r="S44" t="n">
-        <v>179.0642404405167</v>
+        <v>179.1266962566148</v>
       </c>
       <c r="T44" t="n">
-        <v>217.3413068505635</v>
+        <v>217.3533046710778</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2404870786908</v>
+        <v>251.2407063421153</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,19 +25916,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.6401586726446</v>
+        <v>136.6416251260792</v>
       </c>
       <c r="H45" t="n">
-        <v>105.4424819723455</v>
+        <v>105.4566448252536</v>
       </c>
       <c r="I45" t="n">
-        <v>75.30587056603773</v>
+        <v>75.35636030051944</v>
       </c>
       <c r="J45" t="n">
-        <v>60.38567383647801</v>
+        <v>60.52422152698378</v>
       </c>
       <c r="K45" t="n">
-        <v>24.26446727624578</v>
+        <v>24.50126734687161</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -25946,19 +25946,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>50.19867974639887</v>
+        <v>50.38587124096644</v>
       </c>
       <c r="R45" t="n">
-        <v>102.0095794356621</v>
+        <v>102.1006281848752</v>
       </c>
       <c r="S45" t="n">
-        <v>158.6185956321397</v>
+        <v>158.6458343615066</v>
       </c>
       <c r="T45" t="n">
-        <v>197.3297003929348</v>
+        <v>197.3356112293665</v>
       </c>
       <c r="U45" t="n">
-        <v>225.8951084960692</v>
+        <v>225.8952049732688</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,49 +25995,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4013072273112</v>
+        <v>167.4025366526095</v>
       </c>
       <c r="H46" t="n">
-        <v>156.9844511959642</v>
+        <v>156.9953819045248</v>
       </c>
       <c r="I46" t="n">
-        <v>137.7174257469304</v>
+        <v>137.7543979186262</v>
       </c>
       <c r="J46" t="n">
-        <v>85.30560176726496</v>
+        <v>85.39252213584972</v>
       </c>
       <c r="K46" t="n">
-        <v>60.50407784266655</v>
+        <v>60.64691470913344</v>
       </c>
       <c r="L46" t="n">
-        <v>47.21651234681205</v>
+        <v>47.39929435887775</v>
       </c>
       <c r="M46" t="n">
-        <v>46.49199706235918</v>
+        <v>46.68471506615329</v>
       </c>
       <c r="N46" t="n">
-        <v>37.44962643244625</v>
+        <v>37.63776203285606</v>
       </c>
       <c r="O46" t="n">
-        <v>55.1090630420067</v>
+        <v>55.28283671961447</v>
       </c>
       <c r="P46" t="n">
-        <v>66.40984011472142</v>
+        <v>66.55853351624533</v>
       </c>
       <c r="Q46" t="n">
-        <v>102.1280016294458</v>
+        <v>102.230949233282</v>
       </c>
       <c r="R46" t="n">
-        <v>150.779588098481</v>
+        <v>150.8348675305268</v>
       </c>
       <c r="S46" t="n">
-        <v>213.7402209877919</v>
+        <v>213.761646517762</v>
       </c>
       <c r="T46" t="n">
-        <v>225.4260812315602</v>
+        <v>225.4313342305617</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2868654220646</v>
+        <v>286.2869324816264</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>271827.8293422183</v>
+        <v>271709.221794009</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>271827.8293422183</v>
+        <v>271709.221794009</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>275808.3602218903</v>
+        <v>275928.726160744</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>276396.8786761126</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>276396.8786761125</v>
+        <v>276016.084663941</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61995.8207271726</v>
+        <v>61968.76988284417</v>
       </c>
       <c r="C2" t="n">
-        <v>61995.8207271726</v>
+        <v>61968.76988284417</v>
       </c>
       <c r="D2" t="n">
-        <v>62903.66110323817</v>
+        <v>62931.11298402938</v>
       </c>
       <c r="E2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="F2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="G2" t="n">
-        <v>63037.88461034144</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="H2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="I2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317953</v>
       </c>
       <c r="J2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="K2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="L2" t="n">
-        <v>63037.88461034144</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="M2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="N2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317953</v>
       </c>
       <c r="O2" t="n">
-        <v>63037.88461034144</v>
+        <v>62951.03685317954</v>
       </c>
       <c r="P2" t="n">
-        <v>63037.88461034145</v>
+        <v>62951.03685317954</v>
       </c>
     </row>
     <row r="3">
@@ -26313,16 +26313,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>308356.16</v>
+        <v>308183.8838205543</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5138.484</v>
+        <v>5446.975876289214</v>
       </c>
       <c r="E3" t="n">
-        <v>803.403</v>
+        <v>109.902156572954</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40603.6</v>
+        <v>40599.70256325733</v>
       </c>
       <c r="C5" t="n">
-        <v>40603.6</v>
+        <v>40599.70256325733</v>
       </c>
       <c r="D5" t="n">
-        <v>40734.4</v>
+        <v>40738.35521735115</v>
       </c>
       <c r="E5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="F5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="G5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="H5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="I5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="J5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="K5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="L5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="M5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="N5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="O5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
       <c r="P5" t="n">
-        <v>7128.6</v>
+        <v>7113.737365803781</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-286963.9392728274</v>
+        <v>-286814.8165009674</v>
       </c>
       <c r="C6" t="n">
-        <v>21392.2207271726</v>
+        <v>21369.06731958684</v>
       </c>
       <c r="D6" t="n">
-        <v>17030.77710323816</v>
+        <v>16745.78189038901</v>
       </c>
       <c r="E6" t="n">
-        <v>55105.88161034146</v>
+        <v>55727.3973308028</v>
       </c>
       <c r="F6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="G6" t="n">
-        <v>55909.28461034144</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="H6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="I6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737575</v>
       </c>
       <c r="J6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="K6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="L6" t="n">
-        <v>55909.28461034144</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="M6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="N6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737575</v>
       </c>
       <c r="O6" t="n">
-        <v>55909.28461034144</v>
+        <v>55837.29948737576</v>
       </c>
       <c r="P6" t="n">
-        <v>55909.28461034146</v>
+        <v>55837.29948737576</v>
       </c>
     </row>
   </sheetData>
@@ -26675,49 +26675,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="C3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="D3" t="n">
-        <v>326</v>
+        <v>326.1814319885848</v>
       </c>
       <c r="E3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="F3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="G3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="H3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="I3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="L3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="M3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="N3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="O3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
       <c r="P3" t="n">
-        <v>327</v>
+        <v>326.3182277891643</v>
       </c>
     </row>
     <row r="4">
@@ -26892,19 +26892,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>6.360213490542208</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.1367958005794776</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26953,31 +26953,31 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -30959,49 +30959,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.286432160804018</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H2" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I2" t="n">
-        <v>49.59517587939698</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J2" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K2" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L2" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M2" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N2" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O2" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P2" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q2" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R2" t="n">
-        <v>80.80884422110552</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S2" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T2" t="n">
-        <v>5.631356783919594</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1029145728643214</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31038,19 +31038,19 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6883018867924523</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H3" t="n">
-        <v>6.647547169811319</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I3" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J3" t="n">
-        <v>65.02943396226415</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K3" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L3" t="n">
         <v>138.5543797798742</v>
@@ -31065,22 +31065,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P3" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q3" t="n">
-        <v>87.8611320754717</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R3" t="n">
-        <v>42.73509433962265</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S3" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T3" t="n">
-        <v>2.774339622641507</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04528301886792452</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31117,49 +31117,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5770491803278683</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H4" t="n">
-        <v>5.130491803278689</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I4" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J4" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K4" t="n">
-        <v>67.04262295081963</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L4" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M4" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N4" t="n">
-        <v>88.30426229508201</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O4" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P4" t="n">
-        <v>69.79147540983601</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q4" t="n">
-        <v>48.31999999999999</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R4" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S4" t="n">
-        <v>10.05639344262294</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T4" t="n">
-        <v>2.465573770491801</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03147540983606559</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.286432160804018</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H5" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I5" t="n">
-        <v>49.59517587939698</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J5" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K5" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L5" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M5" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N5" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O5" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P5" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q5" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R5" t="n">
-        <v>80.80884422110552</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S5" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T5" t="n">
-        <v>5.631356783919594</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1029145728643214</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,19 +31275,19 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6883018867924523</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H6" t="n">
-        <v>6.647547169811319</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I6" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J6" t="n">
-        <v>65.02943396226415</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K6" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L6" t="n">
         <v>138.5543797798742</v>
@@ -31302,22 +31302,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q6" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R6" t="n">
-        <v>42.73509433962265</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S6" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T6" t="n">
-        <v>2.774339622641507</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04528301886792452</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5770491803278683</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H7" t="n">
-        <v>5.130491803278689</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I7" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J7" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K7" t="n">
-        <v>67.04262295081963</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L7" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M7" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N7" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O7" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P7" t="n">
-        <v>69.79147540983601</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q7" t="n">
-        <v>48.31999999999999</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R7" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S7" t="n">
-        <v>10.05639344262294</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T7" t="n">
-        <v>2.465573770491801</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03147540983606559</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.310552763819094</v>
+        <v>1.311282138647576</v>
       </c>
       <c r="H8" t="n">
-        <v>13.4216984924623</v>
+        <v>13.42916820242449</v>
       </c>
       <c r="I8" t="n">
-        <v>50.52508542713569</v>
+        <v>50.55320465021072</v>
       </c>
       <c r="J8" t="n">
-        <v>111.231527638191</v>
+        <v>111.2934324150398</v>
       </c>
       <c r="K8" t="n">
-        <v>166.7072261306533</v>
+        <v>166.8000053439917</v>
       </c>
       <c r="L8" t="n">
-        <v>206.8150552763819</v>
+        <v>206.9301560946275</v>
       </c>
       <c r="M8" t="n">
-        <v>230.1215979899497</v>
+        <v>230.2496698278014</v>
       </c>
       <c r="N8" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>220.8133969849246</v>
+        <v>220.9362884380569</v>
       </c>
       <c r="P8" t="n">
-        <v>188.4591256281407</v>
+        <v>188.5640106401949</v>
       </c>
       <c r="Q8" t="n">
-        <v>141.5249547738693</v>
+        <v>141.6037190498785</v>
       </c>
       <c r="R8" t="n">
-        <v>82.32401005025126</v>
+        <v>82.36982664182088</v>
       </c>
       <c r="S8" t="n">
-        <v>29.86422110552765</v>
+        <v>29.88084173443167</v>
       </c>
       <c r="T8" t="n">
-        <v>5.736944723618088</v>
+        <v>5.740137561929767</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1048442211055275</v>
+        <v>0.1049025710918061</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,19 +31512,19 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7012075471698112</v>
+        <v>0.701597797107522</v>
       </c>
       <c r="H9" t="n">
-        <v>6.772188679245284</v>
+        <v>6.775957672064753</v>
       </c>
       <c r="I9" t="n">
-        <v>24.14245283018868</v>
+        <v>24.15588906707916</v>
       </c>
       <c r="J9" t="n">
-        <v>66.24873584905662</v>
+        <v>66.28560591005761</v>
       </c>
       <c r="K9" t="n">
-        <v>113.229641509434</v>
+        <v>113.2926583162616</v>
       </c>
       <c r="L9" t="n">
         <v>138.5543797798742</v>
@@ -31539,22 +31539,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>133.8998867924528</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>89.5085283018868</v>
+        <v>89.55834336411107</v>
       </c>
       <c r="R9" t="n">
-        <v>43.53637735849058</v>
+        <v>43.56060708707933</v>
       </c>
       <c r="S9" t="n">
-        <v>13.02462264150943</v>
+        <v>13.03187136294015</v>
       </c>
       <c r="T9" t="n">
-        <v>2.826358490566036</v>
+        <v>2.827931471674616</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04613207547169813</v>
+        <v>0.04615774980970541</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5878688524590162</v>
+        <v>0.5881960248974479</v>
       </c>
       <c r="H10" t="n">
-        <v>5.226688524590166</v>
+        <v>5.229597384997313</v>
       </c>
       <c r="I10" t="n">
-        <v>17.67881967213115</v>
+        <v>17.68865863964326</v>
       </c>
       <c r="J10" t="n">
-        <v>41.56232786885246</v>
+        <v>41.58545896024957</v>
       </c>
       <c r="K10" t="n">
-        <v>68.29967213114752</v>
+        <v>68.33768361990347</v>
       </c>
       <c r="L10" t="n">
-        <v>87.40006557377049</v>
+        <v>87.44870719248058</v>
       </c>
       <c r="M10" t="n">
-        <v>92.15111475409834</v>
+        <v>92.20240052096993</v>
       </c>
       <c r="N10" t="n">
-        <v>89.95996721311481</v>
+        <v>90.01003351907953</v>
       </c>
       <c r="O10" t="n">
-        <v>83.09259016393445</v>
+        <v>83.13883450095931</v>
       </c>
       <c r="P10" t="n">
-        <v>71.10006557377045</v>
+        <v>71.13963559305131</v>
       </c>
       <c r="Q10" t="n">
-        <v>49.226</v>
+        <v>49.2533962302763</v>
       </c>
       <c r="R10" t="n">
-        <v>26.4327213114754</v>
+        <v>26.44743217402524</v>
       </c>
       <c r="S10" t="n">
-        <v>10.24495081967213</v>
+        <v>10.25065254298552</v>
       </c>
       <c r="T10" t="n">
-        <v>2.511803278688523</v>
+        <v>2.513201197289095</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03206557377049184</v>
+        <v>0.03208341953986083</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H11" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I11" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J11" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K11" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L11" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M11" t="n">
-        <v>230.3462332272728</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P11" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q11" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R11" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S11" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T11" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,19 +31749,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H12" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I12" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J12" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K12" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -31779,19 +31779,19 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R12" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S12" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T12" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H13" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I13" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J13" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K13" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L13" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M13" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N13" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O13" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P13" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q13" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R13" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S13" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T13" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,22 +31907,22 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H14" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I14" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J14" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K14" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L14" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M14" t="n">
         <v>230.3462332272727</v>
@@ -31931,25 +31931,25 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P14" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q14" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R14" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S14" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T14" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,19 +31986,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H15" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I15" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J15" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K15" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -32016,19 +32016,19 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R15" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S15" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T15" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H16" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I16" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J16" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K16" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L16" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M16" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N16" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O16" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P16" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q16" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R16" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S16" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T16" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,22 +32144,22 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H17" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I17" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J17" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K17" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L17" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M17" t="n">
         <v>230.3462332272727</v>
@@ -32168,25 +32168,25 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P17" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q17" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R17" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S17" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T17" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,19 +32223,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H18" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I18" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J18" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K18" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
@@ -32253,19 +32253,19 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R18" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S18" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T18" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H19" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I19" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J19" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K19" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L19" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M19" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N19" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O19" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P19" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q19" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R19" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S19" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T19" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H20" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I20" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J20" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K20" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L20" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M20" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P20" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q20" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R20" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S20" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T20" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,19 +32460,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H21" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I21" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J21" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K21" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -32484,25 +32484,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143303</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R21" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S21" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T21" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H22" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I22" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J22" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K22" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L22" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M22" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N22" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O22" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P22" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q22" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R22" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S22" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T22" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,22 +32618,22 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H23" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I23" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J23" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K23" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L23" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M23" t="n">
         <v>230.3462332272727</v>
@@ -32642,25 +32642,25 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P23" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q23" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R23" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S23" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T23" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,19 +32697,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H24" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I24" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J24" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K24" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -32721,25 +32721,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R24" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S24" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T24" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H25" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I25" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J25" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K25" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L25" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M25" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N25" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O25" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P25" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q25" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R25" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S25" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T25" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H26" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I26" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J26" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K26" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L26" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272728</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P26" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q26" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R26" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S26" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T26" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,19 +32934,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H27" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I27" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J27" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K27" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
@@ -32958,25 +32958,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R27" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S27" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T27" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H28" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I28" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J28" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K28" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L28" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M28" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N28" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O28" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P28" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q28" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R28" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S28" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T28" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U28" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H29" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I29" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J29" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K29" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L29" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M29" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N29" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P29" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q29" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R29" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S29" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T29" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,19 +33171,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H30" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I30" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J30" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K30" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
@@ -33192,28 +33192,28 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833334</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R30" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S30" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T30" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H31" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I31" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J31" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K31" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L31" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M31" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N31" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O31" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P31" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q31" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R31" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S31" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T31" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U31" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,22 +33329,22 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H32" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I32" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J32" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K32" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L32" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M32" t="n">
         <v>230.3462332272727</v>
@@ -33353,25 +33353,25 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P32" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q32" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R32" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S32" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T32" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,19 +33408,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H33" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I33" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J33" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K33" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
@@ -33438,19 +33438,19 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R33" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S33" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T33" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H34" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I34" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J34" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K34" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L34" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M34" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N34" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O34" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P34" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q34" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R34" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S34" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T34" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U34" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H35" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I35" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J35" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K35" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L35" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272728</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N35" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P35" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q35" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R35" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S35" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T35" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,19 +33645,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H36" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I36" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J36" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K36" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
@@ -33666,28 +33666,28 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833334</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R36" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S36" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T36" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H37" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I37" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J37" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K37" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L37" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M37" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N37" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O37" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P37" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q37" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R37" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S37" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T37" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U37" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H38" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I38" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J38" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K38" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L38" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M38" t="n">
-        <v>230.3462332272728</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N38" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P38" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q38" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R38" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S38" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T38" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,19 +33882,19 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H39" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I39" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J39" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K39" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L39" t="n">
         <v>138.5543797798742</v>
@@ -33903,28 +33903,28 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833334</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143303</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R39" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S39" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T39" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U39" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H40" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I40" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J40" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K40" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L40" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M40" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N40" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O40" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P40" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q40" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R40" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S40" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T40" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U40" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H41" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I41" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J41" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K41" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L41" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272728</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N41" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P41" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q41" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R41" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S41" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T41" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H42" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I42" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J42" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K42" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220184</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833334</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143303</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R42" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S42" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T42" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H43" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I43" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J43" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K43" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L43" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M43" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N43" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O43" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P43" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q43" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R43" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S43" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T43" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U43" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.314572864321607</v>
+        <v>1.311832071514227</v>
       </c>
       <c r="H44" t="n">
-        <v>13.46286934673366</v>
+        <v>13.43480020239508</v>
       </c>
       <c r="I44" t="n">
-        <v>50.68007035175881</v>
+        <v>50.57440593705229</v>
       </c>
       <c r="J44" t="n">
-        <v>111.5727286432161</v>
+        <v>111.3401072796808</v>
       </c>
       <c r="K44" t="n">
-        <v>167.2185979899498</v>
+        <v>166.869958866878</v>
       </c>
       <c r="L44" t="n">
-        <v>207.4494572864322</v>
+        <v>207.0169396254816</v>
       </c>
       <c r="M44" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N44" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>221.4907386934673</v>
+        <v>221.0289459393429</v>
       </c>
       <c r="P44" t="n">
-        <v>189.0372211055276</v>
+        <v>188.6430916738354</v>
       </c>
       <c r="Q44" t="n">
-        <v>141.95908040201</v>
+        <v>141.6631056127321</v>
       </c>
       <c r="R44" t="n">
-        <v>82.57653768844222</v>
+        <v>82.40437136225565</v>
       </c>
       <c r="S44" t="n">
-        <v>29.95582914572865</v>
+        <v>29.89337332963048</v>
       </c>
       <c r="T44" t="n">
-        <v>5.754542713567838</v>
+        <v>5.742544893053533</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1051658291457285</v>
+        <v>0.1049465657211382</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7033584905660377</v>
+        <v>0.7018920371314099</v>
       </c>
       <c r="H45" t="n">
-        <v>6.792962264150945</v>
+        <v>6.778799411242828</v>
       </c>
       <c r="I45" t="n">
-        <v>24.21650943396227</v>
+        <v>24.16601969948056</v>
       </c>
       <c r="J45" t="n">
-        <v>66.45195283018869</v>
+        <v>66.31340513968291</v>
       </c>
       <c r="K45" t="n">
-        <v>113.5769716981132</v>
+        <v>113.3401716274874</v>
       </c>
       <c r="L45" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
-        <v>142.1340339220184</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N45" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>142.5962444444445</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q45" t="n">
-        <v>89.78309433962265</v>
+        <v>89.59590284505508</v>
       </c>
       <c r="R45" t="n">
-        <v>43.66992452830191</v>
+        <v>43.57887577908878</v>
       </c>
       <c r="S45" t="n">
-        <v>13.0645754716981</v>
+        <v>13.03733674233122</v>
       </c>
       <c r="T45" t="n">
-        <v>2.835028301886791</v>
+        <v>2.829117465455112</v>
       </c>
       <c r="U45" t="n">
-        <v>0.0462735849056604</v>
+        <v>0.04617710770601383</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5896721311475409</v>
+        <v>0.5884427058493126</v>
       </c>
       <c r="H46" t="n">
-        <v>5.242721311475413</v>
+        <v>5.231790602914801</v>
       </c>
       <c r="I46" t="n">
-        <v>17.73304918032787</v>
+        <v>17.69607700863206</v>
       </c>
       <c r="J46" t="n">
-        <v>41.68981967213114</v>
+        <v>41.60289930354639</v>
       </c>
       <c r="K46" t="n">
-        <v>68.50918032786883</v>
+        <v>68.36634346140194</v>
       </c>
       <c r="L46" t="n">
-        <v>87.66816393442623</v>
+        <v>87.48538192236053</v>
       </c>
       <c r="M46" t="n">
-        <v>92.43378688524588</v>
+        <v>92.24106888145177</v>
       </c>
       <c r="N46" t="n">
-        <v>90.23591803278694</v>
+        <v>90.04778243237713</v>
       </c>
       <c r="O46" t="n">
-        <v>83.34747540983609</v>
+        <v>83.17370173222832</v>
       </c>
       <c r="P46" t="n">
-        <v>71.3181639344262</v>
+        <v>71.16947053290228</v>
       </c>
       <c r="Q46" t="n">
-        <v>49.377</v>
+        <v>49.2740523961638</v>
       </c>
       <c r="R46" t="n">
-        <v>26.51380327868851</v>
+        <v>26.45852384664272</v>
       </c>
       <c r="S46" t="n">
-        <v>10.27637704918032</v>
+        <v>10.25495151921029</v>
       </c>
       <c r="T46" t="n">
-        <v>2.51950819672131</v>
+        <v>2.514255197719789</v>
       </c>
       <c r="U46" t="n">
-        <v>0.03216393442622954</v>
+        <v>0.032096874864508</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
